--- a/quizzes/025_histamine_intolerance_quiz--quizzes.xlsx
+++ b/quizzes/025_histamine_intolerance_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'very_frequent'}</t>
+          <t>very_frequent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Very frequent'}</t>
+          <t>Very frequent</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'some_of_the_time'}</t>
+          <t>some_of_the_time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Some of the time'}</t>
+          <t>Some of the time</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'very_frequent'}</t>
+          <t>very_frequent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'Very frequent'}</t>
+          <t>Very frequent</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_32,_'label':_'some_of_the_time'}</t>
+          <t>some_of_the_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 32, 'label': 'Some of the time'}</t>
+          <t>Some of the time</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_33,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 33, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_41,_'label':_'very_frequent'}</t>
+          <t>very_frequent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 41, 'label': 'Very frequent'}</t>
+          <t>Very frequent</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_42,_'label':_'some_of_the_time'}</t>
+          <t>some_of_the_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 42, 'label': 'Some of the time'}</t>
+          <t>Some of the time</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_43,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 43, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_51,_'label':_'very_frequent'}</t>
+          <t>very_frequent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 51, 'label': 'Very frequent'}</t>
+          <t>Very frequent</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_52,_'label':_'some_of_the_time'}</t>
+          <t>some_of_the_time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 52, 'label': 'Some of the time'}</t>
+          <t>Some of the time</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_53,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 53, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
